--- a/SelecciónDatasetsProyecto/EDGAR_GHG/EDGAR_GHG_metadatos.xlsx
+++ b/SelecciónDatasetsProyecto/EDGAR_GHG/EDGAR_GHG_metadatos.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha.de.generacion</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12</t>
+    <t xml:space="preserve">2026-10-08</t>
   </si>
   <si>
     <t xml:space="preserve">N.observaciones</t>
